--- a/phylogenies/Species_information.xlsx
+++ b/phylogenies/Species_information.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jax/🔬Research/2024 - fungal_annotations/fungal_sRNA_annotations/phylogenies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jax/🔬Research/🔍2024 - fungal_sRNA_annotations/phylogenies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E37F10D-3CD3-A347-816B-2D08390573AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3A96BC-8375-6347-8FDE-892B80E5B931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="1540" windowWidth="28800" windowHeight="18000" xr2:uid="{063D12AA-F3DC-8D49-A3A0-2F44CA381166}"/>
+    <workbookView xWindow="34900" yWindow="140" windowWidth="28800" windowHeight="18000" xr2:uid="{063D12AA-F3DC-8D49-A3A0-2F44CA381166}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="339">
   <si>
     <t>Ascosphaera apis</t>
   </si>
@@ -995,9 +995,6 @@
     <t>lifestyle</t>
   </si>
   <si>
-    <t>Magnaporthe oryzae</t>
-  </si>
-  <si>
     <t>Paracoccidioides brasiliensis</t>
   </si>
   <si>
@@ -1014,6 +1011,48 @@
   </si>
   <si>
     <t>Carnivore</t>
+  </si>
+  <si>
+    <t>Funneliformis mosseae</t>
+  </si>
+  <si>
+    <t>Fumos</t>
+  </si>
+  <si>
+    <t>Isaria fumosorosea</t>
+  </si>
+  <si>
+    <t>Metarhizium anisopliae</t>
+  </si>
+  <si>
+    <t>Paraglomus occultum</t>
+  </si>
+  <si>
+    <t>Pichia fermentans</t>
+  </si>
+  <si>
+    <t>Pyricularia oryzae</t>
+  </si>
+  <si>
+    <t>Ustilago maydis</t>
+  </si>
+  <si>
+    <t>Isfum</t>
+  </si>
+  <si>
+    <t>Meani</t>
+  </si>
+  <si>
+    <t>Paocc</t>
+  </si>
+  <si>
+    <t>Pifer</t>
+  </si>
+  <si>
+    <t>Usmay</t>
+  </si>
+  <si>
+    <t>Corn smut</t>
   </si>
 </sst>
 </file>
@@ -1116,10 +1155,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{55A210D0-23B2-1848-88B1-CAF0C9FABBF7}" name="Table1" displayName="Table1" ref="A1:N94" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:N94" xr:uid="{55A210D0-23B2-1848-88B1-CAF0C9FABBF7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M94">
-    <sortCondition ref="B1:B94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{55A210D0-23B2-1848-88B1-CAF0C9FABBF7}" name="Table1" displayName="Table1" ref="A1:N100" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:N100" xr:uid="{55A210D0-23B2-1848-88B1-CAF0C9FABBF7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M100">
+    <sortCondition ref="B1:B100"/>
   </sortState>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{0D024533-DFA7-0A4F-84DF-71D2BDC7E5AB}" name="Species"/>
@@ -1438,7 +1477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB3DC3A-733E-BE49-BA0B-7ED842D78587}">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
@@ -1494,7 +1533,7 @@
         <v>318</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -1546,7 +1585,7 @@
         <v>45</v>
       </c>
       <c r="N3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -1578,7 +1617,7 @@
         <v>45</v>
       </c>
       <c r="N4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -1613,7 +1652,7 @@
         <v>122</v>
       </c>
       <c r="N5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -1645,7 +1684,7 @@
         <v>45</v>
       </c>
       <c r="N6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -1680,7 +1719,7 @@
         <v>45</v>
       </c>
       <c r="N7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1700,7 +1739,7 @@
         <v>314</v>
       </c>
       <c r="N8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -1735,7 +1774,7 @@
         <v>45</v>
       </c>
       <c r="N9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1787,7 +1826,7 @@
         <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1825,7 +1864,7 @@
         <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -1845,7 +1884,7 @@
         <v>314</v>
       </c>
       <c r="N13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1883,7 +1922,7 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -1918,7 +1957,7 @@
         <v>45</v>
       </c>
       <c r="N15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1938,7 +1977,7 @@
         <v>314</v>
       </c>
       <c r="N16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -1976,7 +2015,7 @@
         <v>45</v>
       </c>
       <c r="N17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -1993,7 +2032,7 @@
         <v>192</v>
       </c>
       <c r="N18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -2013,7 +2052,7 @@
         <v>314</v>
       </c>
       <c r="N19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -2103,7 +2142,7 @@
         <v>45</v>
       </c>
       <c r="N22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -2141,7 +2180,7 @@
         <v>45</v>
       </c>
       <c r="N23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -2176,7 +2215,7 @@
         <v>45</v>
       </c>
       <c r="N24" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -2214,7 +2253,7 @@
         <v>45</v>
       </c>
       <c r="N25" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -2234,7 +2273,7 @@
         <v>314</v>
       </c>
       <c r="N26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -2251,7 +2290,7 @@
         <v>192</v>
       </c>
       <c r="N27" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -2286,7 +2325,7 @@
         <v>45</v>
       </c>
       <c r="N28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -2303,7 +2342,7 @@
         <v>99</v>
       </c>
       <c r="N29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -2338,7 +2377,7 @@
         <v>45</v>
       </c>
       <c r="N30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -2355,7 +2394,7 @@
         <v>99</v>
       </c>
       <c r="N31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
@@ -2393,7 +2432,7 @@
         <v>45</v>
       </c>
       <c r="N32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
@@ -2410,7 +2449,7 @@
         <v>99</v>
       </c>
       <c r="N33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -2448,7 +2487,7 @@
         <v>45</v>
       </c>
       <c r="N34" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2483,7 +2522,7 @@
         <v>45</v>
       </c>
       <c r="N35" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
@@ -2518,7 +2557,7 @@
         <v>45</v>
       </c>
       <c r="N36" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
@@ -2629,7 +2668,7 @@
         <v>45</v>
       </c>
       <c r="N39" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
@@ -2667,7 +2706,7 @@
         <v>316</v>
       </c>
       <c r="N40" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
@@ -2702,7 +2741,7 @@
         <v>45</v>
       </c>
       <c r="N41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -2719,12 +2758,12 @@
         <v>99</v>
       </c>
       <c r="N42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B43" t="s">
         <v>295</v>
@@ -2760,7 +2799,7 @@
         <v>45</v>
       </c>
       <c r="N43" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
@@ -2795,7 +2834,7 @@
         <v>45</v>
       </c>
       <c r="N44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
@@ -2815,7 +2854,7 @@
         <v>191</v>
       </c>
       <c r="N45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -2853,7 +2892,7 @@
         <v>122</v>
       </c>
       <c r="N46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -2888,7 +2927,7 @@
         <v>45</v>
       </c>
       <c r="N47" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -2998,7 +3037,7 @@
         <v>191</v>
       </c>
       <c r="N51" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
@@ -3033,7 +3072,7 @@
         <v>45</v>
       </c>
       <c r="N52" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
@@ -3053,12 +3092,12 @@
         <v>191</v>
       </c>
       <c r="N53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B54" t="s">
         <v>75</v>
@@ -3088,7 +3127,7 @@
         <v>45</v>
       </c>
       <c r="N54" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
@@ -3123,7 +3162,7 @@
         <v>45</v>
       </c>
       <c r="N55" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
@@ -3187,7 +3226,7 @@
         <v>45</v>
       </c>
       <c r="N57" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
@@ -3204,7 +3243,7 @@
         <v>99</v>
       </c>
       <c r="N58" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
@@ -3262,7 +3301,7 @@
         <v>313</v>
       </c>
       <c r="N60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
@@ -3300,7 +3339,7 @@
         <v>313</v>
       </c>
       <c r="N61" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
@@ -3349,7 +3388,7 @@
         <v>122</v>
       </c>
       <c r="N63" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
@@ -3366,7 +3405,7 @@
         <v>99</v>
       </c>
       <c r="N64" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
@@ -3404,7 +3443,7 @@
         <v>45</v>
       </c>
       <c r="N65" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
@@ -3421,7 +3460,7 @@
         <v>99</v>
       </c>
       <c r="N66" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
@@ -3569,7 +3608,7 @@
         <v>45</v>
       </c>
       <c r="N71" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
@@ -3604,7 +3643,7 @@
         <v>45</v>
       </c>
       <c r="N72" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
@@ -3808,7 +3847,7 @@
         <v>45</v>
       </c>
       <c r="N78" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
@@ -3843,7 +3882,7 @@
         <v>45</v>
       </c>
       <c r="N79" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
@@ -3887,7 +3926,7 @@
         <v>317</v>
       </c>
       <c r="N80" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
@@ -3928,7 +3967,7 @@
         <v>45</v>
       </c>
       <c r="N81" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
@@ -4080,7 +4119,7 @@
         <v>45</v>
       </c>
       <c r="N85" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
@@ -4121,7 +4160,7 @@
         <v>45</v>
       </c>
       <c r="N86" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
@@ -4173,7 +4212,7 @@
         <v>99</v>
       </c>
       <c r="N88" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
@@ -4190,7 +4229,7 @@
         <v>99</v>
       </c>
       <c r="N89" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
@@ -4225,99 +4264,168 @@
         <v>45</v>
       </c>
       <c r="N90" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="B91" t="s">
-        <v>310</v>
-      </c>
-      <c r="G91" t="s">
-        <v>46</v>
-      </c>
-      <c r="I91" t="s">
-        <v>99</v>
+        <v>326</v>
       </c>
       <c r="N91" t="s">
-        <v>322</v>
+        <v>151</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s">
-        <v>311</v>
-      </c>
-      <c r="G92" t="s">
-        <v>110</v>
-      </c>
-      <c r="M92" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="N92" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s">
-        <v>312</v>
-      </c>
-      <c r="G93" t="s">
-        <v>110</v>
-      </c>
-      <c r="M93" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="N93" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
+        <v>329</v>
+      </c>
+      <c r="B94" t="s">
+        <v>335</v>
+      </c>
+      <c r="N94" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>330</v>
+      </c>
+      <c r="B95" t="s">
+        <v>336</v>
+      </c>
+      <c r="N95" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>332</v>
+      </c>
+      <c r="B96" t="s">
+        <v>337</v>
+      </c>
+      <c r="D96" t="s">
+        <v>338</v>
+      </c>
+      <c r="N96" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>278</v>
+      </c>
+      <c r="B97" t="s">
+        <v>310</v>
+      </c>
+      <c r="G97" t="s">
+        <v>46</v>
+      </c>
+      <c r="I97" t="s">
+        <v>99</v>
+      </c>
+      <c r="N97" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>279</v>
+      </c>
+      <c r="B98" t="s">
+        <v>311</v>
+      </c>
+      <c r="G98" t="s">
+        <v>110</v>
+      </c>
+      <c r="M98" t="s">
+        <v>315</v>
+      </c>
+      <c r="N98" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>280</v>
+      </c>
+      <c r="B99" t="s">
+        <v>312</v>
+      </c>
+      <c r="G99" t="s">
+        <v>110</v>
+      </c>
+      <c r="M99" t="s">
+        <v>315</v>
+      </c>
+      <c r="N99" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
         <v>44</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B100" t="s">
         <v>95</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C100" t="s">
         <v>186</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D100" t="s">
         <v>187</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E100" t="s">
         <v>188</v>
       </c>
-      <c r="F94" t="s">
-        <v>96</v>
-      </c>
-      <c r="G94" t="s">
-        <v>46</v>
-      </c>
-      <c r="H94" t="s">
+      <c r="F100" t="s">
+        <v>96</v>
+      </c>
+      <c r="G100" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" t="s">
         <v>148</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I100" t="s">
         <v>99</v>
       </c>
-      <c r="J94" t="s">
-        <v>96</v>
-      </c>
-      <c r="K94" t="s">
-        <v>123</v>
-      </c>
-      <c r="L94" t="s">
-        <v>45</v>
-      </c>
-      <c r="N94" t="s">
-        <v>322</v>
+      <c r="J100" t="s">
+        <v>96</v>
+      </c>
+      <c r="K100" t="s">
+        <v>123</v>
+      </c>
+      <c r="L100" t="s">
+        <v>45</v>
+      </c>
+      <c r="N100" t="s">
+        <v>321</v>
       </c>
     </row>
   </sheetData>
